--- a/config/trainer/attr_skills.xlsx
+++ b/config/trainer/attr_skills.xlsx
@@ -1731,7 +1731,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>会心耐性</t>
+          <t>暴击抗性</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>PvPダメージ上昇</t>
+          <t>PvP伤害上升</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PvPダメージ耐性</t>
+          <t>PvP抗伤害能力</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
